--- a/02_Study_Selection/Included_and_Excluded_Research_Articles_recap.xlsx
+++ b/02_Study_Selection/Included_and_Excluded_Research_Articles_recap.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_Progetti_PC\2026_SLR_CoWork\SLR_Database\02_Study Selection and Quality Assessment Process\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_Progetti_PC\2026_SLR_CoWork\SLR_VirtualizationMicrocontrollers\02_Study_Selection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17750DC8-86F5-4E81-928A-D7AF3BC8F306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B3413D-C450-4919-8C69-411F43DD370D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="34776" windowHeight="21096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1040,7 +1040,7 @@
         <v>4719</v>
       </c>
       <c r="G3" s="5">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>99</v>
@@ -1066,7 +1066,7 @@
         <v>493</v>
       </c>
       <c r="G4" s="5">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>99</v>
